--- a/Debbirarti's work/Priority Round Robin (Q6).xlsx
+++ b/Debbirarti's work/Priority Round Robin (Q6).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\henry\source\repos\ArchOSC-Assaignment-HenryCox-secondary\archosc-portfolio-HenryCox07\Debbirarti's work\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3DA24723-CC73-45F9-810C-6D97BB62EDB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B09C921-DC26-425F-8518-435BA4062BBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{6A155275-B2EF-430B-9DD0-DB02FCC7282C}"/>
   </bookViews>
